--- a/Specifications/Planning.xlsx
+++ b/Specifications/Planning.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Linje\Documents\Project\An-Era-of-the-Seas\Specifications\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Linje\Documents\An-Era-of-the-Seas\Specifications\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F17180-ADBE-4618-81F0-B24219E427F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85062E1D-B953-40AE-BDD7-4767BB6E2571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="40">
   <si>
     <t>Date Limite</t>
   </si>
@@ -192,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -204,6 +204,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -484,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.6640625" customWidth="1"/>
@@ -546,13 +549,13 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
@@ -726,50 +729,53 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
-        <v>45648</v>
+        <v>45641</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C15" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E15" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
-        <v>45655</v>
+        <v>45648</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16" s="1">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="D16" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E16" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
-        <v>45654</v>
+        <v>45655</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17" s="1">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D17" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="E17" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -777,16 +783,13 @@
         <v>45654</v>
       </c>
       <c r="B18" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C18" s="1">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="D18" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -794,30 +797,30 @@
         <v>45654</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="C19" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
-        <v>45296</v>
+        <v>45654</v>
       </c>
       <c r="B20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C20" s="1">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="D20" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
@@ -828,13 +831,13 @@
         <v>45296</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C21" s="1">
-        <v>0.8</v>
+        <v>0.25</v>
       </c>
       <c r="D21" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
@@ -845,16 +848,16 @@
         <v>45296</v>
       </c>
       <c r="B22" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C22" s="1">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="D22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" t="s">
         <v>9</v>
-      </c>
-      <c r="E22" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -862,10 +865,10 @@
         <v>45296</v>
       </c>
       <c r="B23" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C23" s="1">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="D23" t="s">
         <v>9</v>
@@ -875,37 +878,37 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="6">
+        <v>45296</v>
+      </c>
+      <c r="B24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="D24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="6">
-        <v>45303</v>
-      </c>
-      <c r="B25" t="s">
-        <v>25</v>
-      </c>
-      <c r="C25" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="D25" t="s">
-        <v>4</v>
-      </c>
-      <c r="E25" t="s">
-        <v>14</v>
-      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="6">
         <v>45303</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C26" s="1">
         <v>0.4</v>
@@ -918,46 +921,46 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="6">
+        <v>45303</v>
+      </c>
+      <c r="B27" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="D27" t="s">
+        <v>4</v>
+      </c>
+      <c r="E27" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="6">
-        <v>45303</v>
-      </c>
-      <c r="B28" t="s">
-        <v>12</v>
-      </c>
-      <c r="C28" s="1">
-        <v>1</v>
-      </c>
-      <c r="D28" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" t="s">
-        <v>14</v>
-      </c>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="6">
-        <v>45310</v>
+        <v>45303</v>
       </c>
       <c r="B29" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C29" s="1">
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E29" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -965,10 +968,10 @@
         <v>45310</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C30" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D30" t="s">
         <v>5</v>
@@ -982,7 +985,7 @@
         <v>45310</v>
       </c>
       <c r="B31" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="C31" s="1">
         <v>0.5</v>
@@ -996,13 +999,13 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="6">
-        <v>45317</v>
+        <v>45310</v>
       </c>
       <c r="B32" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="C32" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D32" t="s">
         <v>5</v>
@@ -1013,10 +1016,10 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="6">
-        <v>45324</v>
+        <v>45317</v>
       </c>
       <c r="B33" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C33" s="1">
         <v>1</v>
@@ -1033,7 +1036,7 @@
         <v>45324</v>
       </c>
       <c r="B34" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="C34" s="1">
         <v>1</v>
@@ -1050,16 +1053,16 @@
         <v>45324</v>
       </c>
       <c r="B35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C35" s="1">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E35" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -1067,13 +1070,16 @@
         <v>45324</v>
       </c>
       <c r="B36" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C36" s="1">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D36" t="s">
-        <v>13</v>
+        <v>4</v>
+      </c>
+      <c r="E36" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -1081,16 +1087,13 @@
         <v>45324</v>
       </c>
       <c r="B37" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C37" s="1">
         <v>0.5</v>
       </c>
       <c r="D37" t="s">
-        <v>4</v>
-      </c>
-      <c r="E37" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -1098,30 +1101,30 @@
         <v>45324</v>
       </c>
       <c r="B38" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C38" s="1">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="D38" t="s">
         <v>4</v>
       </c>
       <c r="E38" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="6">
-        <v>45331</v>
+        <v>45324</v>
       </c>
       <c r="B39" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C39" s="1">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="D39" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E39" t="s">
         <v>14</v>
@@ -1129,13 +1132,13 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="6">
-        <v>45338</v>
+        <v>45331</v>
       </c>
       <c r="B40" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C40" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D40" t="s">
         <v>9</v>
@@ -1149,13 +1152,13 @@
         <v>45338</v>
       </c>
       <c r="B41" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C41" s="1">
         <v>0.5</v>
       </c>
       <c r="D41" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E41" t="s">
         <v>14</v>
@@ -1163,30 +1166,33 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="6">
-        <v>45345</v>
+        <v>45338</v>
       </c>
       <c r="B42" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C42" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D42" t="s">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="E42" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="6">
-        <v>45353</v>
+        <v>45345</v>
       </c>
       <c r="B43" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C43" s="1">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D43" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -1194,16 +1200,13 @@
         <v>45353</v>
       </c>
       <c r="B44" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C44" s="1">
         <v>0.8</v>
       </c>
       <c r="D44" t="s">
-        <v>4</v>
-      </c>
-      <c r="E44" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -1211,93 +1214,93 @@
         <v>45353</v>
       </c>
       <c r="B45" t="s">
+        <v>22</v>
+      </c>
+      <c r="C45" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="D45" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="6">
+        <v>45353</v>
+      </c>
+      <c r="B46" t="s">
         <v>29</v>
       </c>
-      <c r="C45" s="1">
+      <c r="C46" s="1">
         <v>0.6</v>
       </c>
-      <c r="D45" t="s">
-        <v>4</v>
-      </c>
-      <c r="E45" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="4" t="s">
+      <c r="D46" t="s">
+        <v>4</v>
+      </c>
+      <c r="E46" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="6">
-        <v>45361</v>
-      </c>
-      <c r="B47" t="s">
-        <v>26</v>
-      </c>
-      <c r="C47" s="1">
-        <v>1</v>
-      </c>
-      <c r="D47" t="s">
-        <v>4</v>
-      </c>
-      <c r="E47" t="s">
-        <v>14</v>
-      </c>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="6">
         <v>45361</v>
       </c>
       <c r="B48" t="s">
+        <v>26</v>
+      </c>
+      <c r="C48" s="1">
+        <v>1</v>
+      </c>
+      <c r="D48" t="s">
+        <v>4</v>
+      </c>
+      <c r="E48" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="6">
+        <v>45361</v>
+      </c>
+      <c r="B49" t="s">
         <v>25</v>
       </c>
-      <c r="C48" s="1">
+      <c r="C49" s="1">
         <v>0.8</v>
       </c>
-      <c r="D48" t="s">
-        <v>4</v>
-      </c>
-      <c r="E48" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="5" t="s">
+      <c r="D49" t="s">
+        <v>4</v>
+      </c>
+      <c r="E49" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B49" s="5"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" s="6">
-        <v>45381</v>
-      </c>
-      <c r="B50" t="s">
-        <v>34</v>
-      </c>
-      <c r="C50" s="1">
-        <v>1</v>
-      </c>
-      <c r="D50" t="s">
-        <v>14</v>
-      </c>
-      <c r="E50" t="s">
-        <v>13</v>
-      </c>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="6">
         <v>45381</v>
       </c>
       <c r="B51" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C51" s="1">
         <v>1</v>
@@ -1306,38 +1309,38 @@
         <v>14</v>
       </c>
       <c r="E51" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="6">
-        <v>45402</v>
+        <v>45381</v>
       </c>
       <c r="B52" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="C52" s="1">
         <v>1</v>
       </c>
       <c r="D52" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="E52" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="6">
-        <v>45416</v>
+        <v>45402</v>
       </c>
       <c r="B53" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C53" s="1">
         <v>1</v>
       </c>
       <c r="D53" t="s">
-        <v>9</v>
-      </c>
-      <c r="E53" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
@@ -1345,13 +1348,13 @@
         <v>45416</v>
       </c>
       <c r="B54" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C54" s="1">
         <v>1</v>
       </c>
       <c r="D54" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E54" t="s">
         <v>14</v>
@@ -1359,40 +1362,66 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="6">
+        <v>45416</v>
+      </c>
+      <c r="B55" t="s">
+        <v>31</v>
+      </c>
+      <c r="C55" s="1">
+        <v>1</v>
+      </c>
+      <c r="D55" t="s">
+        <v>4</v>
+      </c>
+      <c r="E55" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="6">
         <v>45437</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B56" t="s">
         <v>25</v>
       </c>
-      <c r="C55" s="1">
-        <v>1</v>
-      </c>
-      <c r="D55" t="s">
-        <v>4</v>
-      </c>
-      <c r="E55" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" s="4" t="s">
+      <c r="C56" s="1">
+        <v>1</v>
+      </c>
+      <c r="D56" t="s">
+        <v>4</v>
+      </c>
+      <c r="E56" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A56:E56"/>
-    <mergeCell ref="A49:E49"/>
+  <mergeCells count="1">
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A46:E46"/>
   </mergeCells>
-  <conditionalFormatting sqref="C1:C1048576">
+  <conditionalFormatting sqref="C1:C14 C16:C1048576">
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{341F7F22-F941-4980-8602-B8F4500D1D37}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C15">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -1401,7 +1430,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{341F7F22-F941-4980-8602-B8F4500D1D37}</x14:id>
+          <x14:id>{15F7121C-0D5D-40F0-B725-D873DAA9AC8F}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -1422,7 +1451,20 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>C1:C1048576</xm:sqref>
+          <xm:sqref>C1:C14 C16:C1048576</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{15F7121C-0D5D-40F0-B725-D873DAA9AC8F}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF63C384"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>C15</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
